--- a/Assets/Excels/CreatureSheet.xlsx
+++ b/Assets/Excels/CreatureSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Devs\ProjectD\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C21679-FFC5-400E-BE7D-30E0087AC03D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B53BD5-062B-4400-80EA-329AD0B2B752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{BE4D1A5F-5D47-4666-90B3-FC203DF5316E}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{BE4D1A5F-5D47-4666-90B3-FC203DF5316E}"/>
   </bookViews>
   <sheets>
     <sheet name="Entities" sheetId="1" r:id="rId1"/>
@@ -39,37 +39,65 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Creature_0000000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>NameKey</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DescKey</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>monster.walker.name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>monster.walker.desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Hp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Atk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DataId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Faction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Undead</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#Humanoid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Human</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>creature_human_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>creature_human_001_name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>creature_human_001_desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>creature_walker_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>creature_walker_001_name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>creature_walker_001_desc</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -454,45 +482,77 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78A075EE-C989-4A55-A963-36A88D7608BC}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.69921875" customWidth="1"/>
-    <col min="2" max="2" width="22.19921875" customWidth="1"/>
-    <col min="3" max="3" width="21.796875" customWidth="1"/>
+    <col min="2" max="2" width="32.8984375" customWidth="1"/>
+    <col min="3" max="3" width="32.5" customWidth="1"/>
+    <col min="4" max="4" width="21.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2">
+      <c r="E4">
         <v>10</v>
       </c>
-      <c r="E2">
+      <c r="F4">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Excels/CreatureSheet.xlsx
+++ b/Assets/Excels/CreatureSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Devs\ProjectD\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B53BD5-062B-4400-80EA-329AD0B2B752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3955802-1335-4E17-9416-8321C0FDAF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{BE4D1A5F-5D47-4666-90B3-FC203DF5316E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{BE4D1A5F-5D47-4666-90B3-FC203DF5316E}"/>
   </bookViews>
   <sheets>
     <sheet name="Entities" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>NameKey</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -53,10 +53,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Atk</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DataId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -98,6 +94,26 @@
   </si>
   <si>
     <t>creature_walker_001_desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DetectRange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackRange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackSpeed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -482,18 +498,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78A075EE-C989-4A55-A963-36A88D7608BC}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.69921875" customWidth="1"/>
     <col min="2" max="2" width="32.8984375" customWidth="1"/>
     <col min="3" max="3" width="32.5" customWidth="1"/>
     <col min="4" max="4" width="21.796875" customWidth="1"/>
+    <col min="7" max="7" width="17.296875" customWidth="1"/>
+    <col min="8" max="8" width="27.796875" customWidth="1"/>
+    <col min="9" max="9" width="15.796875" customWidth="1"/>
+    <col min="10" max="10" width="17.3984375" customWidth="1"/>
+    <col min="11" max="11" width="16.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -502,32 +523,44 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>3</v>
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
       </c>
       <c r="E3">
         <v>10</v>
@@ -535,25 +568,49 @@
       <c r="F3">
         <v>2</v>
       </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
       <c r="F4">
         <v>1</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excels/CreatureSheet.xlsx
+++ b/Assets/Excels/CreatureSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Devs\ProjectD\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3955802-1335-4E17-9416-8321C0FDAF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E46695-1AEB-4D78-9D38-21EE46E857C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{BE4D1A5F-5D47-4666-90B3-FC203DF5316E}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{BE4D1A5F-5D47-4666-90B3-FC203DF5316E}"/>
   </bookViews>
   <sheets>
     <sheet name="Entities" sheetId="1" r:id="rId1"/>

--- a/Assets/Excels/CreatureSheet.xlsx
+++ b/Assets/Excels/CreatureSheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Devs\ProjectD\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E46695-1AEB-4D78-9D38-21EE46E857C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5215F6D6-B34A-4A98-848A-8435E97A1377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{BE4D1A5F-5D47-4666-90B3-FC203DF5316E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>NameKey</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,10 +61,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Undead</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>#Humanoid</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -73,30 +69,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>creature_human_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>creature_human_001_name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>creature_human_001_desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>creature_walker_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>creature_walker_001_name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>creature_walker_001_desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DetectRange</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -114,6 +86,26 @@
   </si>
   <si>
     <t>MoveSpeed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>creature_dwarf_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>creature_dwarf_001_name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>creature_dwarf_001_desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AIType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ground</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -498,13 +490,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78A075EE-C989-4A55-A963-36A88D7608BC}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.69921875" customWidth="1"/>
     <col min="2" max="2" width="32.8984375" customWidth="1"/>
     <col min="3" max="3" width="32.5" customWidth="1"/>
     <col min="4" max="4" width="21.796875" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13.09765625" customWidth="1"/>
     <col min="7" max="7" width="17.296875" customWidth="1"/>
     <col min="8" max="8" width="27.796875" customWidth="1"/>
     <col min="9" max="9" width="15.796875" customWidth="1"/>
@@ -512,7 +506,7 @@
     <col min="11" max="11" width="16.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -529,38 +523,41 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="H1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="D3" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
       </c>
       <c r="E3">
         <v>10</v>
@@ -580,37 +577,8 @@
       <c r="J3">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>10</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2.5</v>
+      <c r="K3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excels/CreatureSheet.xlsx
+++ b/Assets/Excels/CreatureSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Devs\ProjectD\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5215F6D6-B34A-4A98-848A-8435E97A1377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E132EB-1EBD-4898-92C4-F3F35C2E7683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{BE4D1A5F-5D47-4666-90B3-FC203DF5316E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>NameKey</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -106,6 +106,22 @@
   </si>
   <si>
     <t>Ground</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>creature_lizard_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>creature_lizard_001_name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>creature_lizard_001_desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -490,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78A075EE-C989-4A55-A963-36A88D7608BC}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.69921875" customWidth="1"/>
@@ -560,24 +576,59 @@
         <v>6</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
         <v>16</v>
       </c>
     </row>

--- a/Assets/Excels/CreatureSheet.xlsx
+++ b/Assets/Excels/CreatureSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Devs\ProjectD\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E132EB-1EBD-4898-92C4-F3F35C2E7683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5B0567-9426-4D36-A87D-1ADC8C490B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{BE4D1A5F-5D47-4666-90B3-FC203DF5316E}"/>
   </bookViews>
@@ -39,32 +39,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
-  <si>
-    <t>NameKey</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DescKey</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>Hp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DataId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Faction</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>#Humanoid</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Human</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -93,14 +77,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>creature_dwarf_001_name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>creature_dwarf_001_desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AIType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -113,15 +89,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>creature_lizard_001_name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>creature_lizard_001_desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Monster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t># Humanoid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dwarf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lizard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -524,56 +516,53 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
         <v>9</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -594,21 +583,18 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -629,7 +615,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excels/CreatureSheet.xlsx
+++ b/Assets/Excels/CreatureSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Devs\ProjectD\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5B0567-9426-4D36-A87D-1ADC8C490B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370BD2DB-7BAC-4B6D-B5FB-6D55A2003173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{BE4D1A5F-5D47-4666-90B3-FC203DF5316E}"/>
   </bookViews>
@@ -565,22 +565,22 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K3" t="s">
         <v>10</v>
@@ -597,22 +597,22 @@
         <v>12</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K4" t="s">
         <v>10</v>
